--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\project-github\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF09596-3F31-4432-AD01-D6B39E5ECC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCF3D59-2A97-4545-A073-CF93CF7E4392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="331">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1179,6 +1179,14 @@
   </si>
   <si>
     <t>鸢尾花书系列与矩阵两个视角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20261008-从小山走出来的人，去看大山的美.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从小山走出来的人，去看大山的美</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2722,7 +2730,8 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.61328125" customWidth="1"/>
-    <col min="2" max="3" width="30.69140625" customWidth="1"/>
+    <col min="2" max="2" width="42.15234375" customWidth="1"/>
+    <col min="3" max="3" width="30.69140625" customWidth="1"/>
     <col min="4" max="5" width="15" style="5" customWidth="1"/>
     <col min="6" max="6" width="38.4609375" customWidth="1"/>
   </cols>
@@ -2942,17 +2951,23 @@
       <c r="A13" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="5" t="e">
+      <c r="B13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C13" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E13" s="5" t="e">
+        <v>- [从小山走出来的人，去看大山的美](随笔/20261008-从小山走出来的人，去看大山的美.md)</v>
+      </c>
+      <c r="E13" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F13" t="e">
+        <v>- [从小山走出来的人，去看大山的美](/随笔/20261008-从小山走出来的人，去看大山的美.md)</v>
+      </c>
+      <c r="F13" t="str">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>- [从小山走出来的人，去看大山的美](../../随笔/20261008-从小山走出来的人，去看大山的美/)</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">

--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\project-github\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCF3D59-2A97-4545-A073-CF93CF7E4392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C084F0-A65F-4EAE-A9E4-228DD15990EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="333">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1187,6 +1187,14 @@
   </si>
   <si>
     <t>从小山走出来的人，去看大山的美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20261012-Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4766,17 +4774,23 @@
       <c r="A34" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="5" t="e">
+      <c r="B34" t="s">
+        <v>331</v>
+      </c>
+      <c r="C34" t="s">
+        <v>332</v>
+      </c>
+      <c r="D34" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E34" s="5" t="e">
+        <v>- [Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂](Python基础库/20261012-Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂.md)</v>
+      </c>
+      <c r="E34" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F34" t="e">
+        <v>- [Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂](/Python基础库/20261012-Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂.md)</v>
+      </c>
+      <c r="F34" t="str">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>- [Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂](../../Python基础库/20261012-Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂/)</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.45">

--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\project-github\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C084F0-A65F-4EAE-A9E4-228DD15990EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8268FCD-1878-4C2C-9A18-C4A385E9C4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="338">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1195,6 +1195,26 @@
   </si>
   <si>
     <t>Python 3.15 正式发布：惰性导入、frozendict、sentinel、Tachyon 剖析器，一次全看懂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20261022-给Agent装上手脚，打通本地、数据集群与云运维.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenClaw使用体验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VibeCoding完全指南：2026年，我们用“感觉”写代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给 Agent 装上手脚：本地控制、数据集群与云运维</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3115,243 +3135,261 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.61328125" customWidth="1"/>
-    <col min="2" max="2" width="36.23046875" customWidth="1"/>
-    <col min="3" max="4" width="19.15234375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="29.61328125" customWidth="1"/>
+    <col min="2" max="3" width="36.23046875" customWidth="1"/>
+    <col min="4" max="5" width="19.15234375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="29.61328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>152</v>
       </c>
       <c r="B2" t="s">
         <v>153</v>
       </c>
-      <c r="C2" s="5" t="str">
+      <c r="D2" s="5" t="str">
         <f>"- ["&amp;LEFT(B2,LEN(B2)-3)&amp;"]("&amp;A2&amp;"/"&amp;B2&amp;")"</f>
         <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="E2" s="5" t="str">
         <f>"- ["&amp;SUBSTITUTE(B2,".md","")&amp;"](/"&amp;A2&amp;"/"&amp;B2&amp;")"</f>
         <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](/大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
       </c>
-      <c r="E2" t="str">
-        <f t="shared" ref="E2:E3" si="0">"- ["&amp;LEFT(B2,LEN(B2)-3)&amp;"](../../"&amp;A2&amp;"/"&amp;LEFT(B2,LEN(B2)-3)&amp;"/)"</f>
+      <c r="F2" t="str">
+        <f t="shared" ref="F2:F3" si="0">"- ["&amp;LEFT(B2,LEN(B2)-3)&amp;"](../../"&amp;A2&amp;"/"&amp;LEFT(B2,LEN(B2)-3)&amp;"/)"</f>
         <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](../../大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块/)</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>152</v>
       </c>
       <c r="B3" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="5" t="str">
-        <f t="shared" ref="C3" si="1">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+      <c r="D3" s="5" t="str">
+        <f t="shared" ref="D3" si="1">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>- [基于DeepSeek，构建个人本地RAG知识库](大模型相关/基于DeepSeek，构建个人本地RAG知识库.md)</v>
       </c>
-      <c r="D3" s="5" t="str">
-        <f t="shared" ref="D3" si="2">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+      <c r="E3" s="5" t="str">
+        <f t="shared" ref="E3" si="2">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>- [基于DeepSeek，构建个人本地RAG知识库](/大模型相关/基于DeepSeek，构建个人本地RAG知识库.md)</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <f t="shared" si="0"/>
         <v>- [基于DeepSeek，构建个人本地RAG知识库](../../大模型相关/基于DeepSeek，构建个人本地RAG知识库/)</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>152</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="str">
-        <f t="shared" ref="C4" si="3">"- ["&amp;LEFT(B4,LEN(B4)-3)&amp;"]("&amp;A4&amp;"/"&amp;B4&amp;")"</f>
+      <c r="D4" s="5" t="str">
+        <f t="shared" ref="D4" si="3">"- ["&amp;LEFT(B4,LEN(B4)-3)&amp;"]("&amp;A4&amp;"/"&amp;B4&amp;")"</f>
         <v>- [Python调用apiKey试玩ChatGPT](大模型相关/Python调用apiKey试玩ChatGPT.md)</v>
       </c>
-      <c r="D4" s="5" t="str">
-        <f t="shared" ref="D4" si="4">"- ["&amp;SUBSTITUTE(B4,".md","")&amp;"](/"&amp;A4&amp;"/"&amp;B4&amp;")"</f>
+      <c r="E4" s="5" t="str">
+        <f t="shared" ref="E4" si="4">"- ["&amp;SUBSTITUTE(B4,".md","")&amp;"](/"&amp;A4&amp;"/"&amp;B4&amp;")"</f>
         <v>- [Python调用apiKey试玩ChatGPT](/大模型相关/Python调用apiKey试玩ChatGPT.md)</v>
       </c>
-      <c r="E4" t="str">
-        <f t="shared" ref="E4" si="5">"- ["&amp;LEFT(B4,LEN(B4)-3)&amp;"](../../"&amp;A4&amp;"/"&amp;LEFT(B4,LEN(B4)-3)&amp;"/)"</f>
+      <c r="F4" t="str">
+        <f t="shared" ref="F4" si="5">"- ["&amp;LEFT(B4,LEN(B4)-3)&amp;"](../../"&amp;A4&amp;"/"&amp;LEFT(B4,LEN(B4)-3)&amp;"/)"</f>
         <v>- [Python调用apiKey试玩ChatGPT](../../大模型相关/Python调用apiKey试玩ChatGPT/)</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>152</v>
       </c>
       <c r="B5" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="5" t="str">
-        <f t="shared" ref="C5" si="6">"- ["&amp;LEFT(B5,LEN(B5)-3)&amp;"]("&amp;A5&amp;"/"&amp;B5&amp;")"</f>
+      <c r="D5" s="5" t="str">
+        <f t="shared" ref="D5" si="6">"- ["&amp;LEFT(B5,LEN(B5)-3)&amp;"]("&amp;A5&amp;"/"&amp;B5&amp;")"</f>
         <v>- [让ChatGPT回答闰年的计算逻辑](大模型相关/让ChatGPT回答闰年的计算逻辑.md)</v>
       </c>
-      <c r="D5" s="5" t="str">
-        <f t="shared" ref="D5" si="7">"- ["&amp;SUBSTITUTE(B5,".md","")&amp;"](/"&amp;A5&amp;"/"&amp;B5&amp;")"</f>
+      <c r="E5" s="5" t="str">
+        <f t="shared" ref="E5" si="7">"- ["&amp;SUBSTITUTE(B5,".md","")&amp;"](/"&amp;A5&amp;"/"&amp;B5&amp;")"</f>
         <v>- [让ChatGPT回答闰年的计算逻辑](/大模型相关/让ChatGPT回答闰年的计算逻辑.md)</v>
       </c>
-      <c r="E5" t="str">
-        <f t="shared" ref="E5" si="8">"- ["&amp;LEFT(B5,LEN(B5)-3)&amp;"](../../"&amp;A5&amp;"/"&amp;LEFT(B5,LEN(B5)-3)&amp;"/)"</f>
+      <c r="F5" t="str">
+        <f t="shared" ref="F5" si="8">"- ["&amp;LEFT(B5,LEN(B5)-3)&amp;"](../../"&amp;A5&amp;"/"&amp;LEFT(B5,LEN(B5)-3)&amp;"/)"</f>
         <v>- [让ChatGPT回答闰年的计算逻辑](../../大模型相关/让ChatGPT回答闰年的计算逻辑/)</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>152</v>
       </c>
       <c r="B8" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="5" t="str">
+      <c r="C8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D8" s="5" t="str">
         <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"]("&amp;A8&amp;"/"&amp;B8&amp;")"</f>
         <v>- [OpenClaw使用体验](大模型相关/20260313-OpenClaw使用体验.md)</v>
       </c>
-      <c r="D8" s="5" t="str">
+      <c r="E8" s="5" t="str">
         <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"](/"&amp;A8&amp;"/"&amp;B8&amp;")"</f>
         <v>- [OpenClaw使用体验](/大模型相关/20260313-OpenClaw使用体验.md)</v>
       </c>
-      <c r="E8" t="str">
-        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"](../../"&amp;A8&amp;"/"&amp;LEFT(B8,LEN(B8)-3)&amp;"/)"</f>
+      <c r="F8" t="str">
+        <f>"- ["&amp;C8&amp;"](../../"&amp;A8&amp;"/"&amp;LEFT(B8,LEN(B8)-3)&amp;"/)"</f>
         <v>- [OpenClaw使用体验](../../大模型相关/20260313-OpenClaw使用体验/)</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="5" t="str">
-        <f t="shared" ref="C9:C14" si="9">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"]("&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+      <c r="C9" t="s">
+        <v>335</v>
+      </c>
+      <c r="D9" s="5" t="str">
+        <f t="shared" ref="D9:D14" si="9">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"]("&amp;A9&amp;"/"&amp;B9&amp;")"</f>
         <v>- [VibeCoding完全指南：2026年，我们用“感觉”写代码](大模型相关/20260320-VibeCoding完全指南：2026年，我们用“感觉”写代码.md)</v>
       </c>
-      <c r="D9" s="5" t="str">
-        <f t="shared" ref="D9:D14" si="10">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](/"&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+      <c r="E9" s="5" t="str">
+        <f t="shared" ref="E9:E14" si="10">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](/"&amp;A9&amp;"/"&amp;B9&amp;")"</f>
         <v>- [VibeCoding完全指南：2026年，我们用“感觉”写代码](/大模型相关/20260320-VibeCoding完全指南：2026年，我们用“感觉”写代码.md)</v>
       </c>
-      <c r="E9" t="str">
-        <f t="shared" ref="E9:E14" si="11">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](../../"&amp;A9&amp;"/"&amp;LEFT(B9,LEN(B9)-3)&amp;"/)"</f>
+      <c r="F9" t="str">
+        <f t="shared" ref="F9:F14" si="11">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](../../"&amp;A9&amp;"/"&amp;LEFT(B9,LEN(B9)-3)&amp;"/)"</f>
         <v>- [VibeCoding完全指南：2026年，我们用“感觉”写代码](../../大模型相关/20260320-VibeCoding完全指南：2026年，我们用“感觉”写代码/)</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>152</v>
       </c>
       <c r="B10" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="5" t="str">
+      <c r="C10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" s="5" t="str">
         <f t="shared" si="9"/>
         <v>- [Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序](大模型相关/20260326-Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序.md)</v>
       </c>
-      <c r="D10" s="5" t="str">
+      <c r="E10" s="5" t="str">
         <f t="shared" si="10"/>
         <v>- [Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序](/大模型相关/20260326-Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序.md)</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <f t="shared" si="11"/>
         <v>- [Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序](../../大模型相关/20260326-Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序/)</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="5" t="e">
+      <c r="B11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D11" s="5" t="e">
+        <v>- [给Agent装上手脚，打通本地、数据集群与云运维](大模型相关/20261022-给Agent装上手脚，打通本地、数据集群与云运维.md)</v>
+      </c>
+      <c r="E11" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E11" t="e">
+        <v>- [给Agent装上手脚，打通本地、数据集群与云运维](/大模型相关/20261022-给Agent装上手脚，打通本地、数据集群与云运维.md)</v>
+      </c>
+      <c r="F11" t="str">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+        <v>- [给Agent装上手脚，打通本地、数据集群与云运维](../../大模型相关/20261022-给Agent装上手脚，打通本地、数据集群与云运维/)</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="5" t="e">
+      <c r="D12" s="5" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="D12" s="5" t="e">
+      <c r="E12" s="5" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="E12" t="e">
+      <c r="F12" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>152</v>
       </c>
-      <c r="C13" s="5" t="e">
+      <c r="D13" s="5" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="D13" s="5" t="e">
+      <c r="E13" s="5" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" t="e">
+      <c r="F13" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>152</v>
       </c>
-      <c r="C14" s="5" t="e">
+      <c r="D14" s="5" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="D14" s="5" t="e">
+      <c r="E14" s="5" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" t="e">
+      <c r="F14" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
